--- a/Job_Scraping_Project/Data/Output/Jobs.xlsx
+++ b/Job_Scraping_Project/Data/Output/Jobs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ana\Documents\facultate\ANUL III\rpa\Job_Scraping_RPAUiPath_Project\Job_Scraping_Project\Data\Output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B23DB07-BFA3-408C-A202-0D9B0C133B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD7CB697-4524-46D2-8F26-13AEB8281250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <x:bookViews>
     <x:workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" firstSheet="0" activeTab="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </x:bookViews>
@@ -26,34 +26,145 @@
     <x:t>Keyword</x:t>
   </x:si>
   <x:si>
-    <x:t>Location</x:t>
+    <x:t>Site</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JobTitle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Company</x:t>
+  </x:si>
+  <x:si>
+    <x:t>City</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Salary</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JobUrl</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ScrapeDate</x:t>
   </x:si>
   <x:si>
     <x:t>QA Engineer</x:t>
   </x:si>
   <x:si>
+    <x:t>eJobs</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TechSoft SRL</x:t>
+  </x:si>
+  <x:si>
     <x:t>Remote</x:t>
   </x:si>
   <x:si>
+    <x:t>6000-8000 RON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://example.com/jobs/qa-engineer-techsoft-001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-01-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BestJobs</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Manual QA Tester</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CloudNova</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bucuresti</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>https://example.com/jobs/manual-qa-cloudnova-014</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-01-01</x:t>
+  </x:si>
+  <x:si>
     <x:t>RPA Developer</x:t>
   </x:si>
   <x:si>
-    <x:t>Bucharest</x:t>
+    <x:t>RPA Developer (UiPath)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AutomationHub</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cluj-Napoca</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9000-12000 RON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://example.com/jobs/rpa-developer-automationhub-210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Negotiable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://example.com/jobs/rpa-developer-automationhub-211</x:t>
   </x:si>
   <x:si>
     <x:t>.NET Developer</x:t>
   </x:si>
   <x:si>
-    <x:t>Java Developer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C++ Developer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Python Developer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cloud Engineer</x:t>
+    <x:t>FinApps</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12000-16000 RON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://example.com/jobs/dotnet-finapps-077</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2025-12-31</x:t>
+  </x:si>
+  <x:si>
+    <x:t>.NET Developer (C#)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://example.com/jobs/dotnet-finapps-078</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QA Automation Engineer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PixelWorks</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Timisoara</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7000-10000 RON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://example.com/jobs/qa-auto-pixelworks-032</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Data Analyst</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Junior Data Analyst</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DataSpring</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Iasi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5000-6500 RON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://example.com/jobs/jr-data-analyst-dataspring-055</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -397,74 +508,247 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:B7"/>
+  <x:dimension ref="A1:H9"/>
   <x:sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <x:cols>
-    <x:col min="1" max="1" width="13.664062" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="21.886719" style="0" customWidth="1"/>
+    <x:col min="2" max="6" width="9.109375" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="74.886719" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="19.109375" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <x:row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <x:c r="C1" s="0" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D1" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E1" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F1" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G1" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H1" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <x:c r="A2" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:2" x14ac:dyDescent="0.3">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="H2" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <x:c r="A3" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:2" x14ac:dyDescent="0.3">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <x:c r="A4" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:2" x14ac:dyDescent="0.3">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <x:c r="A5" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:2" x14ac:dyDescent="0.3">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <x:c r="A6" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <x:c r="A7" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <x:c r="A8" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <x:c r="A7" s="0" t="s">
+      <x:c r="B8" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:2">
-      <x:c r="A8" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>5</x:v>
+      <x:c r="C8" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <x:c r="A9" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Job_Scraping_Project/Data/Output/Jobs.xlsx
+++ b/Job_Scraping_Project/Data/Output/Jobs.xlsx
@@ -23,15 +23,12 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
-    <x:t>Keyword</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Site</x:t>
-  </x:si>
-  <x:si>
     <x:t>JobTitle</x:t>
   </x:si>
   <x:si>
+    <x:t>JobUrl</x:t>
+  </x:si>
+  <x:si>
     <x:t>Company</x:t>
   </x:si>
   <x:si>
@@ -41,25 +38,25 @@
     <x:t>Salary</x:t>
   </x:si>
   <x:si>
-    <x:t>JobUrl</x:t>
-  </x:si>
-  <x:si>
     <x:t>ScrapeDate</x:t>
   </x:si>
   <x:si>
-    <x:t>QA Engineer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>eJobs</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TechSoft SRL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Remote</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6000-8000 RON</x:t>
+    <x:t>Agent / Broker Imobiliar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.ejobs.ro/user/locuri-de-munca/agent-broker-imobiliar/1925107</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FREIM ESTATE S.R.L.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>București, Ilfov</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1400 - 4500 EUR net / lună</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13 Ian. 2026</x:t>
   </x:si>
   <x:si>
     <x:t>https://example.com/jobs/qa-engineer-techsoft-001</x:t>
@@ -68,19 +65,19 @@
     <x:t>2026-01-02</x:t>
   </x:si>
   <x:si>
-    <x:t>BestJobs</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Manual QA Tester</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CloudNova</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bucuresti</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
+    <x:t>Frigotehnist</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.ejobs.ro/user/locuri-de-munca/frigotehnist/1927004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUMANCENTRIC HR S.R.L.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>București</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5000 - 9000 RON net / lună</x:t>
   </x:si>
   <x:si>
     <x:t>https://example.com/jobs/manual-qa-cloudnova-014</x:t>
@@ -89,37 +86,55 @@
     <x:t>2026-01-01</x:t>
   </x:si>
   <x:si>
-    <x:t>RPA Developer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RPA Developer (UiPath)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AutomationHub</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cluj-Napoca</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9000-12000 RON</x:t>
+    <x:t>Agent Vanzari in teren</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.ejobs.ro/user/locuri-de-munca/agent-vanzari-in-teren/1923848</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C&amp;M Jeler</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Satu-Mare, Oradea, Brasov, București</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4000 RON net / lună</x:t>
   </x:si>
   <x:si>
     <x:t>https://example.com/jobs/rpa-developer-automationhub-210</x:t>
   </x:si>
   <x:si>
-    <x:t>Negotiable</x:t>
+    <x:t>https://www.ejobs.ro/user/locuri-de-munca/agent-de-turism-bucuresti/1926831</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKY GDS S.R.L.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cluj-Napoca, Floresti, Gilau și alte 22 orașe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4000 - 6500 RON net / lună</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Agent Imobiliar si Specialist Marketing</x:t>
   </x:si>
   <x:si>
     <x:t>https://example.com/jobs/rpa-developer-automationhub-211</x:t>
   </x:si>
   <x:si>
-    <x:t>.NET Developer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FinApps</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12000-16000 RON</x:t>
+    <x:t>https://www.ejobs.ro/user/locuri-de-munca/agent-imobiliar-si-specialist-marketing/1923945</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLASS GLOBAL CONCEPT S.R.L.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>București, Voluntari</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1500 - 10000 EUR net / lună</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Agent Imobiliar</x:t>
   </x:si>
   <x:si>
     <x:t>https://example.com/jobs/dotnet-finapps-077</x:t>
@@ -128,43 +143,169 @@
     <x:t>2025-12-31</x:t>
   </x:si>
   <x:si>
-    <x:t>.NET Developer (C#)</x:t>
+    <x:t>https://www.ejobs.ro/user/locuri-de-munca/agent-imobiliar/1926755</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SC. BLITZ NETWORK SA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>București, Ilfov, Voluntari și alte 2 orașe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Agent Vanzari - Tunari (Jud. Ilfov)</x:t>
   </x:si>
   <x:si>
     <x:t>https://example.com/jobs/dotnet-finapps-078</x:t>
   </x:si>
   <x:si>
-    <x:t>QA Automation Engineer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PixelWorks</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Timisoara</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7000-10000 RON</x:t>
+    <x:t>https://www.ejobs.ro/user/locuri-de-munca/agent-vanzari-tunari-jud-ilfov/1926125</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SC LICURICI IMPEX SRL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Customer Support Analyst with French (Hybrid)</x:t>
   </x:si>
   <x:si>
     <x:t>https://example.com/jobs/qa-auto-pixelworks-032</x:t>
   </x:si>
   <x:si>
-    <x:t>Data Analyst</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Junior Data Analyst</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DataSpring</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Iasi</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5000-6500 RON</x:t>
+    <x:t>https://www.ejobs.ro/user/locuri-de-munca/customer-support-analyst-with-french-hybrid/1925508</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ascensos Contact Centres Romania SRL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>București, Ilfov, Măgurele (Ilfov) și alte 2 orașe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5500 RON net / lună</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Agent Vânzări – Piese &amp; Service pentru utilaje</x:t>
   </x:si>
   <x:si>
     <x:t>https://example.com/jobs/jr-data-analyst-dataspring-055</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Agent Vânzări</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.ejobs.ro/user/locuri-de-munca/agent-vanzari/1924935</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASOCIATIA OAMENILOR DE AFACERI EUROASIA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3000 - 4000 RON net / lună</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12 Ian. 2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.ejobs.ro/user/locuri-de-munca/agent-vanzari-piese-service-pentru-utilaje/1925381</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Industrial Total Diesel S.R.L.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tata Bebe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3200 - 5000 RON net / lună</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Consultant vânzări/Sales Reprezentative Orange Store</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Operator sala jocuri / Agent Servicii Client venit 3700-3750 lei net+bonus+tips</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.ejobs.ro/user/locuri-de-munca/operator-sala-jocuri-agent-servicii-client-venit-lei-net-bonus-tips/1924300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAX BET SRL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Agent Imobiliar / Real Estate Consultant Bucuresti</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3700 - 3750 RON net / lună</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11 Ian. 2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8 Ian. 2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.ejobs.ro/user/locuri-de-munca/agent-imobiliar-real-estate-consultant-bucuresti/1926420</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R&amp;D ADVISERS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>București, Voluntari, Ilfov și alte 2 orașe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2500 - 5000 EUR net / lună</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4000 - 8000 RON net / lună</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.ejobs.ro/user/locuri-de-munca/consultant-vanzari-sales-reprezentative-orange-store/1926349</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cellular One</x:t>
+  </x:si>
+  <x:si>
+    <x:t>București, Iasi, Tulcea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.ejobs.ro/user/locuri-de-munca/agent-vanzari-horeca/1926224</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Agent Vanzari HoReCa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGENT DE TURISM - BUCUREŞTI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15000 - 20000 RON net / lună</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1000 - 1500 EUR net / lună</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Agent imobiliar cu/fara experienta</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.ejobs.ro/user/locuri-de-munca/agent-imobiliar-cu-fara-experienta/1926039</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CR Imobiliare</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5000 - 15000 RON net / lună</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7 Ian. 2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Reprezentant B2B</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.ejobs.ro/user/locuri-de-munca/reprezentant-bb/1924115</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DRUCKFARBEN ROMANIA SRL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4500 - 6000 RON net / lună</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16 Dec. 2025</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -537,41 +678,41 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G1" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H1" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <x:c r="A2" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="E2" s="0" t="s">
+      <x:c r="F2" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="F2" s="0" t="s">
+      <x:c r="G2" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="G2" s="0" t="s">
+      <x:c r="H2" s="0" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="H2" s="0" t="s">
-        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <x:c r="A3" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>15</x:v>
@@ -586,21 +727,21 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G3" s="0" t="s">
+      <x:c r="H3" s="0" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="H3" s="0" t="s">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <x:c r="A4" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
         <x:v>22</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>9</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
         <x:v>23</x:v>
@@ -612,143 +753,303 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <x:c r="A5" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <x:c r="A6" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <x:c r="A7" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <x:c r="A8" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <x:c r="A9" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:8">
+      <x:c r="A10" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:8">
+      <x:c r="A11" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:8">
+      <x:c r="A12" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="G9" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>14</x:v>
+      <x:c r="E12" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:8">
+      <x:c r="A13" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:8">
+      <x:c r="A14" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F14" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:8">
+      <x:c r="A15" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="F15" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:8">
+      <x:c r="A16" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E16" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="F16" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:8">
+      <x:c r="A17" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="F17" s="0" t="s">
+        <x:v>94</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
